--- a/output.xlsx
+++ b/output.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SI UPertamina\laptop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A719696-7C19-4B9B-93A5-C7E3304DD6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA171B97-0309-4D76-9D88-5066E121AF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Output" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="654">
   <si>
     <t>no</t>
   </si>
@@ -1924,22 +1935,64 @@
     <t>role_is_admin</t>
   </si>
   <si>
+    <t>Nabil</t>
+  </si>
+  <si>
+    <t>qwerty</t>
+  </si>
+  <si>
+    <t>albert.ltp@universitaspertamina.ac.id</t>
+  </si>
+  <si>
+    <t>zxcvbnm</t>
+  </si>
+  <si>
+    <t>asdfghjkl</t>
+  </si>
+  <si>
+    <t>qwertyuiop</t>
+  </si>
+  <si>
+    <t>Albert</t>
+  </si>
+  <si>
+    <t>Nabil tamvan</t>
+  </si>
+  <si>
+    <t>brader</t>
+  </si>
+  <si>
+    <t>nabilazizi631@gmail.com</t>
+  </si>
+  <si>
+    <t>acoc69839@gmail.com</t>
+  </si>
+  <si>
+    <t>robotsinga75@gmail.com</t>
+  </si>
+  <si>
+    <t>QEE123</t>
+  </si>
+  <si>
+    <t>SCBKEREN</t>
+  </si>
+  <si>
+    <t>PIM5</t>
+  </si>
+  <si>
+    <t>no_lama</t>
+  </si>
+  <si>
+    <t>no_baru</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
-    <t>admin123</t>
-  </si>
-  <si>
     <t>TIK@universitaspertamina.ac.id</t>
-  </si>
-  <si>
-    <t>Nabil</t>
-  </si>
-  <si>
-    <t>qwerty</t>
-  </si>
-  <si>
-    <t>albert.ltp@universitaspertamina.ac.id</t>
   </si>
 </sst>
 </file>
@@ -1955,16 +2008,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFCE9178"/>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1989,14 +2042,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2337,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8.875" bestFit="1" customWidth="1"/>
@@ -2347,7 +2401,7 @@
     <col min="6" max="6" width="80.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2369,12 +2423,18 @@
       <c r="G1" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="H1" t="s">
+        <v>650</v>
+      </c>
+      <c r="I1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
@@ -2389,15 +2449,23 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <f>A2+12</f>
+        <v>13</v>
+      </c>
+      <c r="I2" s="3">
+        <f>H2+1</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
@@ -2412,15 +2480,23 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <f>I2+1</f>
+        <v>15</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I66" si="0">H3+1</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
@@ -2435,15 +2511,23 @@
       <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4:H67" si="1">I3+1</f>
+        <v>17</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -2458,15 +2542,23 @@
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
@@ -2481,15 +2573,23 @@
       <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
@@ -2504,15 +2604,23 @@
       <c r="F7" t="s">
         <v>8</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
@@ -2527,15 +2635,23 @@
       <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
@@ -2550,15 +2666,23 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C10" t="s">
@@ -2573,15 +2697,23 @@
       <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C11" t="s">
@@ -2596,15 +2728,23 @@
       <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C12" t="s">
@@ -2619,15 +2759,23 @@
       <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C13" t="s">
@@ -2642,15 +2790,23 @@
       <c r="F13" t="s">
         <v>13</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C14" t="s">
@@ -2665,15 +2821,23 @@
       <c r="F14" t="s">
         <v>13</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C15" t="s">
@@ -2688,15 +2852,23 @@
       <c r="F15" t="s">
         <v>61</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C16" t="s">
@@ -2711,15 +2883,23 @@
       <c r="F16" t="s">
         <v>13</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C17" t="s">
@@ -2734,15 +2914,23 @@
       <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C18" t="s">
@@ -2757,15 +2945,23 @@
       <c r="F18" t="s">
         <v>8</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C19" t="s">
@@ -2780,15 +2976,23 @@
       <c r="F19" t="s">
         <v>8</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C20" t="s">
@@ -2803,15 +3007,23 @@
       <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C21" t="s">
@@ -2826,15 +3038,23 @@
       <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C22" t="s">
@@ -2849,15 +3069,23 @@
       <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C23" t="s">
@@ -2872,15 +3100,23 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C24" t="s">
@@ -2895,15 +3131,23 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C25" t="s">
@@ -2918,15 +3162,23 @@
       <c r="F25" t="s">
         <v>13</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C26" t="s">
@@ -2941,15 +3193,23 @@
       <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C27" t="s">
@@ -2964,15 +3224,23 @@
       <c r="F27" t="s">
         <v>13</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C28" t="s">
@@ -2987,15 +3255,23 @@
       <c r="F28" t="s">
         <v>61</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>113</v>
       </c>
       <c r="C29" t="s">
@@ -3010,15 +3286,23 @@
       <c r="F29" t="s">
         <v>13</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C30" t="s">
@@ -3033,15 +3317,23 @@
       <c r="F30" t="s">
         <v>13</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C31" t="s">
@@ -3056,15 +3348,23 @@
       <c r="F31" t="s">
         <v>13</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C32" t="s">
@@ -3079,15 +3379,23 @@
       <c r="F32" t="s">
         <v>13</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C33" t="s">
@@ -3102,15 +3410,23 @@
       <c r="F33" t="s">
         <v>61</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C34" t="s">
@@ -3125,15 +3441,23 @@
       <c r="F34" t="s">
         <v>13</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C35" t="s">
@@ -3148,15 +3472,23 @@
       <c r="F35" t="s">
         <v>8</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C36" t="s">
@@ -3171,15 +3503,23 @@
       <c r="F36" t="s">
         <v>13</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C37" t="s">
@@ -3194,15 +3534,23 @@
       <c r="F37" t="s">
         <v>13</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C38" t="s">
@@ -3217,15 +3565,23 @@
       <c r="F38" t="s">
         <v>13</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C39" t="s">
@@ -3240,15 +3596,23 @@
       <c r="F39" t="s">
         <v>8</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C40" t="s">
@@ -3263,15 +3627,23 @@
       <c r="F40" t="s">
         <v>8</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C41" t="s">
@@ -3286,15 +3658,23 @@
       <c r="F41" t="s">
         <v>13</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C42" t="s">
@@ -3309,15 +3689,23 @@
       <c r="F42" t="s">
         <v>13</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C43" t="s">
@@ -3332,15 +3720,23 @@
       <c r="F43" t="s">
         <v>13</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C44" t="s">
@@ -3355,15 +3751,23 @@
       <c r="F44" t="s">
         <v>13</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>176</v>
       </c>
       <c r="C45" t="s">
@@ -3378,15 +3782,23 @@
       <c r="F45" t="s">
         <v>13</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C46" t="s">
@@ -3401,15 +3813,23 @@
       <c r="F46" t="s">
         <v>13</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>184</v>
       </c>
       <c r="C47" t="s">
@@ -3424,15 +3844,23 @@
       <c r="F47" t="s">
         <v>8</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C48" t="s">
@@ -3447,15 +3875,23 @@
       <c r="F48" t="s">
         <v>13</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="0"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C49" t="s">
@@ -3470,15 +3906,23 @@
       <c r="F49" t="s">
         <v>13</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="I49" s="3">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C50" t="s">
@@ -3493,15 +3937,23 @@
       <c r="F50" t="s">
         <v>8</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C51" t="s">
@@ -3516,15 +3968,23 @@
       <c r="F51" t="s">
         <v>13</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C52" t="s">
@@ -3539,15 +3999,23 @@
       <c r="F52" t="s">
         <v>13</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="0"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C53" t="s">
@@ -3556,15 +4024,23 @@
       <c r="D53" t="s">
         <v>210</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C54" t="s">
@@ -3579,15 +4055,23 @@
       <c r="F54" t="s">
         <v>13</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C55" t="s">
@@ -3602,15 +4086,23 @@
       <c r="F55" t="s">
         <v>13</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C56" t="s">
@@ -3625,15 +4117,23 @@
       <c r="F56" t="s">
         <v>13</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="0"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C57" t="s">
@@ -3648,15 +4148,23 @@
       <c r="F57" t="s">
         <v>13</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58">
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="0"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>227</v>
       </c>
       <c r="C58" t="s">
@@ -3671,15 +4179,23 @@
       <c r="F58" t="s">
         <v>13</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="I58" s="3">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>231</v>
       </c>
       <c r="C59" t="s">
@@ -3694,15 +4210,23 @@
       <c r="F59" t="s">
         <v>13</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="I59" s="3">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>235</v>
       </c>
       <c r="C60" t="s">
@@ -3717,15 +4241,23 @@
       <c r="F60" t="s">
         <v>13</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C61" t="s">
@@ -3740,15 +4272,23 @@
       <c r="F61" t="s">
         <v>13</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62">
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="I61" s="3">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="3" t="s">
         <v>243</v>
       </c>
       <c r="C62" t="s">
@@ -3763,15 +4303,23 @@
       <c r="F62" t="s">
         <v>13</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="I62" s="3">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>247</v>
       </c>
       <c r="C63" t="s">
@@ -3786,15 +4334,23 @@
       <c r="F63" t="s">
         <v>13</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64">
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="I63" s="3">
+        <f t="shared" si="0"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>251</v>
       </c>
       <c r="C64" t="s">
@@ -3809,15 +4365,23 @@
       <c r="F64" t="s">
         <v>13</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="I64" s="3">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>255</v>
       </c>
       <c r="C65" t="s">
@@ -3832,15 +4396,23 @@
       <c r="F65" t="s">
         <v>13</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66">
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="I65" s="3">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C66" t="s">
@@ -3855,15 +4427,23 @@
       <c r="F66" t="s">
         <v>13</v>
       </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67">
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" si="1"/>
+        <v>141</v>
+      </c>
+      <c r="I66" s="3">
+        <f t="shared" si="0"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>263</v>
       </c>
       <c r="C67" t="s">
@@ -3878,15 +4458,23 @@
       <c r="F67" t="s">
         <v>13</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68">
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="I67" s="3">
+        <f t="shared" ref="I67:I130" si="2">H67+1</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>267</v>
       </c>
       <c r="C68" t="s">
@@ -3901,15 +4489,23 @@
       <c r="F68" t="s">
         <v>13</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <f t="shared" ref="H68:H131" si="3">I67+1</f>
+        <v>145</v>
+      </c>
+      <c r="I68" s="3">
+        <f t="shared" si="2"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>271</v>
       </c>
       <c r="C69" t="s">
@@ -3924,15 +4520,23 @@
       <c r="F69" t="s">
         <v>13</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70">
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" si="3"/>
+        <v>147</v>
+      </c>
+      <c r="I69" s="3">
+        <f t="shared" si="2"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>275</v>
       </c>
       <c r="C70" t="s">
@@ -3947,15 +4551,23 @@
       <c r="F70" t="s">
         <v>13</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71">
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+      <c r="I70" s="3">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="3" t="s">
         <v>279</v>
       </c>
       <c r="C71" t="s">
@@ -3970,15 +4582,23 @@
       <c r="F71" t="s">
         <v>13</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72">
+      <c r="G71" s="3">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3">
+        <f t="shared" si="3"/>
+        <v>151</v>
+      </c>
+      <c r="I71" s="3">
+        <f t="shared" si="2"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="3" t="s">
         <v>283</v>
       </c>
       <c r="C72" t="s">
@@ -3993,15 +4613,23 @@
       <c r="F72" t="s">
         <v>13</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73">
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" si="3"/>
+        <v>153</v>
+      </c>
+      <c r="I72" s="3">
+        <f t="shared" si="2"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="3" t="s">
         <v>287</v>
       </c>
       <c r="C73" t="s">
@@ -4016,15 +4644,23 @@
       <c r="F73" t="s">
         <v>13</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74">
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <f t="shared" si="3"/>
+        <v>155</v>
+      </c>
+      <c r="I73" s="3">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="3" t="s">
         <v>291</v>
       </c>
       <c r="C74" t="s">
@@ -4039,15 +4675,23 @@
       <c r="F74" t="s">
         <v>13</v>
       </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="G74" s="3">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" si="3"/>
+        <v>157</v>
+      </c>
+      <c r="I74" s="3">
+        <f t="shared" si="2"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>295</v>
       </c>
       <c r="C75" t="s">
@@ -4062,15 +4706,23 @@
       <c r="F75" t="s">
         <v>13</v>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76">
+      <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="I75" s="3">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>299</v>
       </c>
       <c r="C76" t="s">
@@ -4085,15 +4737,23 @@
       <c r="F76" t="s">
         <v>13</v>
       </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77">
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <f t="shared" si="3"/>
+        <v>161</v>
+      </c>
+      <c r="I76" s="3">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="3" t="s">
         <v>303</v>
       </c>
       <c r="C77" t="s">
@@ -4108,15 +4768,23 @@
       <c r="F77" t="s">
         <v>13</v>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78">
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <f t="shared" si="3"/>
+        <v>163</v>
+      </c>
+      <c r="I77" s="3">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="3" t="s">
         <v>307</v>
       </c>
       <c r="C78" t="s">
@@ -4131,15 +4799,23 @@
       <c r="F78" t="s">
         <v>8</v>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+      <c r="I78" s="3">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="3" t="s">
         <v>311</v>
       </c>
       <c r="C79" t="s">
@@ -4154,15 +4830,23 @@
       <c r="F79" t="s">
         <v>13</v>
       </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80">
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <f t="shared" si="3"/>
+        <v>167</v>
+      </c>
+      <c r="I79" s="3">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="3" t="s">
         <v>315</v>
       </c>
       <c r="C80" t="s">
@@ -4177,15 +4861,23 @@
       <c r="F80" t="s">
         <v>13</v>
       </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="G80" s="3">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="I80" s="3">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="3" t="s">
         <v>319</v>
       </c>
       <c r="C81" t="s">
@@ -4200,15 +4892,23 @@
       <c r="F81" t="s">
         <v>13</v>
       </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82">
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <f t="shared" si="3"/>
+        <v>171</v>
+      </c>
+      <c r="I81" s="3">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="3" t="s">
         <v>323</v>
       </c>
       <c r="C82" t="s">
@@ -4223,15 +4923,23 @@
       <c r="F82" t="s">
         <v>13</v>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+      <c r="I82" s="3">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="3" t="s">
         <v>327</v>
       </c>
       <c r="C83" t="s">
@@ -4246,15 +4954,23 @@
       <c r="F83" t="s">
         <v>13</v>
       </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84">
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+      <c r="I83" s="3">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="3" t="s">
         <v>331</v>
       </c>
       <c r="C84" t="s">
@@ -4269,15 +4985,23 @@
       <c r="F84" t="s">
         <v>13</v>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="G84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
+        <f t="shared" si="3"/>
+        <v>177</v>
+      </c>
+      <c r="I84" s="3">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="3" t="s">
         <v>335</v>
       </c>
       <c r="C85" t="s">
@@ -4292,15 +5016,23 @@
       <c r="F85" t="s">
         <v>13</v>
       </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86">
+      <c r="G85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3">
+        <f t="shared" si="3"/>
+        <v>179</v>
+      </c>
+      <c r="I85" s="3">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>339</v>
       </c>
       <c r="C86" t="s">
@@ -4315,15 +5047,23 @@
       <c r="F86" t="s">
         <v>13</v>
       </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87">
+      <c r="G86" s="3">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3">
+        <f t="shared" si="3"/>
+        <v>181</v>
+      </c>
+      <c r="I86" s="3">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="3" t="s">
         <v>343</v>
       </c>
       <c r="C87" t="s">
@@ -4338,15 +5078,23 @@
       <c r="F87" t="s">
         <v>13</v>
       </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88">
+      <c r="G87" s="3">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3">
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="I87" s="3">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="3" t="s">
         <v>347</v>
       </c>
       <c r="C88" t="s">
@@ -4361,15 +5109,23 @@
       <c r="F88" t="s">
         <v>13</v>
       </c>
-      <c r="G88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89">
+      <c r="G88" s="3">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="I88" s="3">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="3" t="s">
         <v>351</v>
       </c>
       <c r="C89" t="s">
@@ -4384,15 +5140,23 @@
       <c r="F89" t="s">
         <v>13</v>
       </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90">
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+      <c r="I89" s="3">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="3" t="s">
         <v>355</v>
       </c>
       <c r="C90" t="s">
@@ -4407,15 +5171,23 @@
       <c r="F90" t="s">
         <v>13</v>
       </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91">
+      <c r="G90" s="3">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3">
+        <f t="shared" si="3"/>
+        <v>189</v>
+      </c>
+      <c r="I90" s="3">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="3" t="s">
         <v>359</v>
       </c>
       <c r="C91" t="s">
@@ -4430,15 +5202,23 @@
       <c r="F91" t="s">
         <v>13</v>
       </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92">
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+      <c r="I91" s="3">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="3" t="s">
         <v>363</v>
       </c>
       <c r="C92" t="s">
@@ -4453,15 +5233,23 @@
       <c r="F92" t="s">
         <v>13</v>
       </c>
-      <c r="G92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93">
+      <c r="G92" s="3">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3">
+        <f t="shared" si="3"/>
+        <v>193</v>
+      </c>
+      <c r="I92" s="3">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="3" t="s">
         <v>367</v>
       </c>
       <c r="C93" t="s">
@@ -4476,15 +5264,23 @@
       <c r="F93" t="s">
         <v>13</v>
       </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="G93" s="3">
+        <v>0</v>
+      </c>
+      <c r="H93" s="3">
+        <f t="shared" si="3"/>
+        <v>195</v>
+      </c>
+      <c r="I93" s="3">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="3" t="s">
         <v>371</v>
       </c>
       <c r="C94" t="s">
@@ -4499,15 +5295,23 @@
       <c r="F94" t="s">
         <v>13</v>
       </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <f t="shared" si="3"/>
+        <v>197</v>
+      </c>
+      <c r="I94" s="3">
+        <f t="shared" si="2"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="3" t="s">
         <v>375</v>
       </c>
       <c r="C95" t="s">
@@ -4522,15 +5326,23 @@
       <c r="F95" t="s">
         <v>13</v>
       </c>
-      <c r="G95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96">
+      <c r="G95" s="3">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3">
+        <f t="shared" si="3"/>
+        <v>199</v>
+      </c>
+      <c r="I95" s="3">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="3" t="s">
         <v>379</v>
       </c>
       <c r="C96" t="s">
@@ -4545,15 +5357,23 @@
       <c r="F96" t="s">
         <v>13</v>
       </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+      <c r="I96" s="3">
+        <f t="shared" si="2"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="3" t="s">
         <v>383</v>
       </c>
       <c r="C97" t="s">
@@ -4568,15 +5388,23 @@
       <c r="F97" t="s">
         <v>13</v>
       </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98">
+      <c r="G97" s="3">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3">
+        <f t="shared" si="3"/>
+        <v>203</v>
+      </c>
+      <c r="I97" s="3">
+        <f t="shared" si="2"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="3" t="s">
         <v>387</v>
       </c>
       <c r="C98" t="s">
@@ -4591,15 +5419,23 @@
       <c r="F98" t="s">
         <v>13</v>
       </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="G98" s="3">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3">
+        <f t="shared" si="3"/>
+        <v>205</v>
+      </c>
+      <c r="I98" s="3">
+        <f t="shared" si="2"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="3" t="s">
         <v>391</v>
       </c>
       <c r="C99" t="s">
@@ -4614,15 +5450,23 @@
       <c r="F99" t="s">
         <v>13</v>
       </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="G99" s="3">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+      <c r="I99" s="3">
+        <f t="shared" si="2"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="3" t="s">
         <v>395</v>
       </c>
       <c r="C100" t="s">
@@ -4637,15 +5481,23 @@
       <c r="F100" t="s">
         <v>13</v>
       </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <f t="shared" si="3"/>
+        <v>209</v>
+      </c>
+      <c r="I100" s="3">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>399</v>
       </c>
       <c r="C101" t="s">
@@ -4660,15 +5512,23 @@
       <c r="F101" t="s">
         <v>13</v>
       </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102">
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+      <c r="I101" s="3">
+        <f t="shared" si="2"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>403</v>
       </c>
       <c r="C102" t="s">
@@ -4683,15 +5543,23 @@
       <c r="F102" t="s">
         <v>61</v>
       </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+      <c r="I102" s="3">
+        <f t="shared" si="2"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>406</v>
       </c>
       <c r="C103" t="s">
@@ -4706,15 +5574,23 @@
       <c r="F103" t="s">
         <v>13</v>
       </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104">
+      <c r="G103" s="3">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+      <c r="I103" s="3">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>410</v>
       </c>
       <c r="C104" t="s">
@@ -4729,15 +5605,23 @@
       <c r="F104" t="s">
         <v>13</v>
       </c>
-      <c r="G104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105">
+      <c r="G104" s="3">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3">
+        <f t="shared" si="3"/>
+        <v>217</v>
+      </c>
+      <c r="I104" s="3">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="3" t="s">
         <v>414</v>
       </c>
       <c r="C105" t="s">
@@ -4752,15 +5636,23 @@
       <c r="F105" t="s">
         <v>13</v>
       </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106">
+      <c r="G105" s="3">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+      <c r="I105" s="3">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="3" t="s">
         <v>418</v>
       </c>
       <c r="C106" t="s">
@@ -4775,15 +5667,23 @@
       <c r="F106" t="s">
         <v>13</v>
       </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107">
+      <c r="G106" s="3">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
+        <f t="shared" si="3"/>
+        <v>221</v>
+      </c>
+      <c r="I106" s="3">
+        <f t="shared" si="2"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="3" t="s">
         <v>422</v>
       </c>
       <c r="C107" t="s">
@@ -4798,15 +5698,23 @@
       <c r="F107" t="s">
         <v>13</v>
       </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108">
+      <c r="G107" s="3">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+      <c r="I107" s="3">
+        <f t="shared" si="2"/>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>426</v>
       </c>
       <c r="C108" t="s">
@@ -4821,15 +5729,23 @@
       <c r="F108" t="s">
         <v>13</v>
       </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109">
+      <c r="G108" s="3">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="I108" s="3">
+        <f t="shared" si="2"/>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="3" t="s">
         <v>430</v>
       </c>
       <c r="C109" t="s">
@@ -4844,15 +5760,23 @@
       <c r="F109" t="s">
         <v>13</v>
       </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110">
+      <c r="G109" s="3">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+      <c r="I109" s="3">
+        <f t="shared" si="2"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>434</v>
       </c>
       <c r="C110" t="s">
@@ -4867,15 +5791,23 @@
       <c r="F110" t="s">
         <v>13</v>
       </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111">
+      <c r="G110" s="3">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+      <c r="I110" s="3">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>438</v>
       </c>
       <c r="C111" t="s">
@@ -4890,15 +5822,23 @@
       <c r="F111" t="s">
         <v>61</v>
       </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112">
+      <c r="G111" s="3">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="I111" s="3">
+        <f t="shared" si="2"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="3" t="s">
         <v>441</v>
       </c>
       <c r="C112" t="s">
@@ -4913,15 +5853,23 @@
       <c r="F112" t="s">
         <v>13</v>
       </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113">
+      <c r="G112" s="3">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3">
+        <f t="shared" si="3"/>
+        <v>233</v>
+      </c>
+      <c r="I112" s="3">
+        <f t="shared" si="2"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="3" t="s">
         <v>445</v>
       </c>
       <c r="C113" t="s">
@@ -4936,15 +5884,23 @@
       <c r="F113" t="s">
         <v>61</v>
       </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114">
+      <c r="G113" s="3">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3">
+        <f t="shared" si="3"/>
+        <v>235</v>
+      </c>
+      <c r="I113" s="3">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="3" t="s">
         <v>448</v>
       </c>
       <c r="C114" t="s">
@@ -4959,15 +5915,23 @@
       <c r="F114" t="s">
         <v>13</v>
       </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115">
+      <c r="G114" s="3">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3">
+        <f t="shared" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="I114" s="3">
+        <f t="shared" si="2"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="3" t="s">
         <v>452</v>
       </c>
       <c r="C115" t="s">
@@ -4982,15 +5946,23 @@
       <c r="F115" t="s">
         <v>13</v>
       </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116">
+      <c r="G115" s="3">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+      <c r="I115" s="3">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="3" t="s">
         <v>456</v>
       </c>
       <c r="C116" t="s">
@@ -5005,15 +5977,23 @@
       <c r="F116" t="s">
         <v>61</v>
       </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117">
+      <c r="G116" s="3">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+      <c r="I116" s="3">
+        <f t="shared" si="2"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="3" t="s">
         <v>459</v>
       </c>
       <c r="C117" t="s">
@@ -5028,15 +6008,23 @@
       <c r="F117" t="s">
         <v>13</v>
       </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118">
+      <c r="G117" s="3">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="I117" s="3">
+        <f t="shared" si="2"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="3" t="s">
         <v>463</v>
       </c>
       <c r="C118" t="s">
@@ -5051,15 +6039,23 @@
       <c r="F118" t="s">
         <v>13</v>
       </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119">
+      <c r="G118" s="3">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+      <c r="I118" s="3">
+        <f t="shared" si="2"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="3" t="s">
         <v>467</v>
       </c>
       <c r="C119" t="s">
@@ -5074,15 +6070,23 @@
       <c r="F119" t="s">
         <v>13</v>
       </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120">
+      <c r="G119" s="3">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3">
+        <f t="shared" si="3"/>
+        <v>247</v>
+      </c>
+      <c r="I119" s="3">
+        <f t="shared" si="2"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="3" t="s">
         <v>471</v>
       </c>
       <c r="C120" t="s">
@@ -5097,15 +6101,23 @@
       <c r="F120" t="s">
         <v>13</v>
       </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121">
+      <c r="G120" s="3">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="I120" s="3">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="3" t="s">
         <v>475</v>
       </c>
       <c r="C121" t="s">
@@ -5120,15 +6132,23 @@
       <c r="F121" t="s">
         <v>13</v>
       </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122">
+      <c r="G121" s="3">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3">
+        <f t="shared" si="3"/>
+        <v>251</v>
+      </c>
+      <c r="I121" s="3">
+        <f t="shared" si="2"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="3" t="s">
         <v>479</v>
       </c>
       <c r="C122" t="s">
@@ -5143,15 +6163,23 @@
       <c r="F122" t="s">
         <v>13</v>
       </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123">
+      <c r="G122" s="3">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3">
+        <f t="shared" si="3"/>
+        <v>253</v>
+      </c>
+      <c r="I122" s="3">
+        <f t="shared" si="2"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="3" t="s">
         <v>483</v>
       </c>
       <c r="C123" t="s">
@@ -5166,15 +6194,23 @@
       <c r="F123" t="s">
         <v>13</v>
       </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124">
+      <c r="G123" s="3">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+      <c r="I123" s="3">
+        <f t="shared" si="2"/>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="3" t="s">
         <v>487</v>
       </c>
       <c r="C124" t="s">
@@ -5189,15 +6225,23 @@
       <c r="F124" t="s">
         <v>13</v>
       </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125">
+      <c r="G124" s="3">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+      <c r="I124" s="3">
+        <f t="shared" si="2"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="3" t="s">
         <v>491</v>
       </c>
       <c r="C125" t="s">
@@ -5212,15 +6256,23 @@
       <c r="F125" t="s">
         <v>13</v>
       </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126">
+      <c r="G125" s="3">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3">
+        <f t="shared" si="3"/>
+        <v>259</v>
+      </c>
+      <c r="I125" s="3">
+        <f t="shared" si="2"/>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="3" t="s">
         <v>495</v>
       </c>
       <c r="C126" t="s">
@@ -5235,15 +6287,23 @@
       <c r="F126" t="s">
         <v>13</v>
       </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127">
+      <c r="G126" s="3">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3">
+        <f t="shared" si="3"/>
+        <v>261</v>
+      </c>
+      <c r="I126" s="3">
+        <f t="shared" si="2"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="3" t="s">
         <v>499</v>
       </c>
       <c r="C127" t="s">
@@ -5258,15 +6318,23 @@
       <c r="F127" t="s">
         <v>13</v>
       </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128">
+      <c r="G127" s="3">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3">
+        <f t="shared" si="3"/>
+        <v>263</v>
+      </c>
+      <c r="I127" s="3">
+        <f t="shared" si="2"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="3" t="s">
         <v>503</v>
       </c>
       <c r="C128" t="s">
@@ -5281,15 +6349,23 @@
       <c r="F128" t="s">
         <v>13</v>
       </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129">
+      <c r="G128" s="3">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3">
+        <f t="shared" si="3"/>
+        <v>265</v>
+      </c>
+      <c r="I128" s="3">
+        <f t="shared" si="2"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="3" t="s">
         <v>507</v>
       </c>
       <c r="C129" t="s">
@@ -5304,15 +6380,23 @@
       <c r="F129" t="s">
         <v>61</v>
       </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130">
+      <c r="G129" s="3">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3">
+        <f t="shared" si="3"/>
+        <v>267</v>
+      </c>
+      <c r="I129" s="3">
+        <f t="shared" si="2"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="3" t="s">
         <v>510</v>
       </c>
       <c r="C130" t="s">
@@ -5327,15 +6411,23 @@
       <c r="F130" t="s">
         <v>13</v>
       </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131">
+      <c r="G130" s="3">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3">
+        <f t="shared" si="3"/>
+        <v>269</v>
+      </c>
+      <c r="I130" s="3">
+        <f t="shared" si="2"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
         <v>514</v>
       </c>
       <c r="C131" t="s">
@@ -5350,15 +6442,23 @@
       <c r="F131" t="s">
         <v>61</v>
       </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132">
+      <c r="G131" s="3">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3">
+        <f t="shared" si="3"/>
+        <v>271</v>
+      </c>
+      <c r="I131" s="3">
+        <f t="shared" ref="I131:I167" si="4">H131+1</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="3" t="s">
         <v>517</v>
       </c>
       <c r="C132" t="s">
@@ -5373,15 +6473,23 @@
       <c r="F132" t="s">
         <v>13</v>
       </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133">
+      <c r="G132" s="3">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3">
+        <f t="shared" ref="H132:H167" si="5">I131+1</f>
+        <v>273</v>
+      </c>
+      <c r="I132" s="3">
+        <f t="shared" si="4"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="3" t="s">
         <v>521</v>
       </c>
       <c r="C133" t="s">
@@ -5396,15 +6504,23 @@
       <c r="F133" t="s">
         <v>61</v>
       </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134">
+      <c r="G133" s="3">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3">
+        <f t="shared" si="5"/>
+        <v>275</v>
+      </c>
+      <c r="I133" s="3">
+        <f t="shared" si="4"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
         <v>524</v>
       </c>
       <c r="C134" t="s">
@@ -5419,15 +6535,23 @@
       <c r="F134" t="s">
         <v>13</v>
       </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135">
+      <c r="G134" s="3">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3">
+        <f t="shared" si="5"/>
+        <v>277</v>
+      </c>
+      <c r="I134" s="3">
+        <f t="shared" si="4"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
         <v>528</v>
       </c>
       <c r="C135" t="s">
@@ -5442,15 +6566,23 @@
       <c r="F135" t="s">
         <v>13</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136">
+      <c r="G135" s="3">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3">
+        <f t="shared" si="5"/>
+        <v>279</v>
+      </c>
+      <c r="I135" s="3">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="3" t="s">
         <v>532</v>
       </c>
       <c r="C136" t="s">
@@ -5465,15 +6597,23 @@
       <c r="F136" t="s">
         <v>536</v>
       </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137">
+      <c r="G136" s="3">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3">
+        <f t="shared" si="5"/>
+        <v>281</v>
+      </c>
+      <c r="I136" s="3">
+        <f t="shared" si="4"/>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="3" t="s">
         <v>537</v>
       </c>
       <c r="C137" t="s">
@@ -5488,15 +6628,23 @@
       <c r="F137" t="s">
         <v>13</v>
       </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138">
+      <c r="G137" s="3">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3">
+        <f t="shared" si="5"/>
+        <v>283</v>
+      </c>
+      <c r="I137" s="3">
+        <f t="shared" si="4"/>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="3" t="s">
         <v>541</v>
       </c>
       <c r="C138" t="s">
@@ -5511,15 +6659,23 @@
       <c r="F138" t="s">
         <v>13</v>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139">
+      <c r="G138" s="3">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3">
+        <f t="shared" si="5"/>
+        <v>285</v>
+      </c>
+      <c r="I138" s="3">
+        <f t="shared" si="4"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="3" t="s">
         <v>545</v>
       </c>
       <c r="C139" t="s">
@@ -5534,15 +6690,23 @@
       <c r="F139" t="s">
         <v>61</v>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140">
+      <c r="G139" s="3">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3">
+        <f t="shared" si="5"/>
+        <v>287</v>
+      </c>
+      <c r="I139" s="3">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="3" t="s">
         <v>548</v>
       </c>
       <c r="C140" t="s">
@@ -5557,15 +6721,23 @@
       <c r="F140" t="s">
         <v>61</v>
       </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141">
+      <c r="G140" s="3">
+        <v>0</v>
+      </c>
+      <c r="H140" s="3">
+        <f t="shared" si="5"/>
+        <v>289</v>
+      </c>
+      <c r="I140" s="3">
+        <f t="shared" si="4"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="3" t="s">
         <v>551</v>
       </c>
       <c r="C141" t="s">
@@ -5580,15 +6752,23 @@
       <c r="F141" t="s">
         <v>536</v>
       </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142">
+      <c r="G141" s="3">
+        <v>0</v>
+      </c>
+      <c r="H141" s="3">
+        <f t="shared" si="5"/>
+        <v>291</v>
+      </c>
+      <c r="I141" s="3">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="3" t="s">
         <v>555</v>
       </c>
       <c r="C142" t="s">
@@ -5603,15 +6783,23 @@
       <c r="F142" t="s">
         <v>13</v>
       </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143">
+      <c r="G142" s="3">
+        <v>0</v>
+      </c>
+      <c r="H142" s="3">
+        <f t="shared" si="5"/>
+        <v>293</v>
+      </c>
+      <c r="I142" s="3">
+        <f t="shared" si="4"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
         <v>142</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="3" t="s">
         <v>559</v>
       </c>
       <c r="C143" t="s">
@@ -5626,15 +6814,23 @@
       <c r="F143" t="s">
         <v>536</v>
       </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144">
+      <c r="G143" s="3">
+        <v>0</v>
+      </c>
+      <c r="H143" s="3">
+        <f t="shared" si="5"/>
+        <v>295</v>
+      </c>
+      <c r="I143" s="3">
+        <f t="shared" si="4"/>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>563</v>
       </c>
       <c r="C144" t="s">
@@ -5649,15 +6845,23 @@
       <c r="F144" t="s">
         <v>61</v>
       </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145">
+      <c r="G144" s="3">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3">
+        <f t="shared" si="5"/>
+        <v>297</v>
+      </c>
+      <c r="I144" s="3">
+        <f t="shared" si="4"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="3" t="s">
         <v>566</v>
       </c>
       <c r="C145" t="s">
@@ -5672,15 +6876,23 @@
       <c r="F145" t="s">
         <v>61</v>
       </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146">
+      <c r="G145" s="3">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3">
+        <f t="shared" si="5"/>
+        <v>299</v>
+      </c>
+      <c r="I145" s="3">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="3" t="s">
         <v>569</v>
       </c>
       <c r="C146" t="s">
@@ -5695,15 +6907,23 @@
       <c r="F146" t="s">
         <v>61</v>
       </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147">
+      <c r="G146" s="3">
+        <v>0</v>
+      </c>
+      <c r="H146" s="3">
+        <f t="shared" si="5"/>
+        <v>301</v>
+      </c>
+      <c r="I146" s="3">
+        <f t="shared" si="4"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C147" t="s">
@@ -5718,15 +6938,23 @@
       <c r="F147" t="s">
         <v>61</v>
       </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148">
+      <c r="G147" s="3">
+        <v>0</v>
+      </c>
+      <c r="H147" s="3">
+        <f t="shared" si="5"/>
+        <v>303</v>
+      </c>
+      <c r="I147" s="3">
+        <f t="shared" si="4"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="3" t="s">
         <v>575</v>
       </c>
       <c r="C148" t="s">
@@ -5741,15 +6969,23 @@
       <c r="F148" t="s">
         <v>61</v>
       </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149">
+      <c r="G148" s="3">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3">
+        <f t="shared" si="5"/>
+        <v>305</v>
+      </c>
+      <c r="I148" s="3">
+        <f t="shared" si="4"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="3" t="s">
         <v>578</v>
       </c>
       <c r="C149" t="s">
@@ -5764,15 +7000,23 @@
       <c r="F149" t="s">
         <v>61</v>
       </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150">
+      <c r="G149" s="3">
+        <v>0</v>
+      </c>
+      <c r="H149" s="3">
+        <f t="shared" si="5"/>
+        <v>307</v>
+      </c>
+      <c r="I149" s="3">
+        <f t="shared" si="4"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="3" t="s">
         <v>581</v>
       </c>
       <c r="C150" t="s">
@@ -5787,15 +7031,23 @@
       <c r="F150" t="s">
         <v>13</v>
       </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151">
+      <c r="G150" s="3">
+        <v>0</v>
+      </c>
+      <c r="H150" s="3">
+        <f t="shared" si="5"/>
+        <v>309</v>
+      </c>
+      <c r="I150" s="3">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
         <v>150</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="3" t="s">
         <v>585</v>
       </c>
       <c r="C151" t="s">
@@ -5810,15 +7062,23 @@
       <c r="F151" t="s">
         <v>13</v>
       </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152">
+      <c r="G151" s="3">
+        <v>0</v>
+      </c>
+      <c r="H151" s="3">
+        <f t="shared" si="5"/>
+        <v>311</v>
+      </c>
+      <c r="I151" s="3">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
         <v>151</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B152" s="3" t="s">
         <v>589</v>
       </c>
       <c r="C152" t="s">
@@ -5833,15 +7093,23 @@
       <c r="F152" t="s">
         <v>13</v>
       </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153">
+      <c r="G152" s="3">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3">
+        <f t="shared" si="5"/>
+        <v>313</v>
+      </c>
+      <c r="I152" s="3">
+        <f t="shared" si="4"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
         <v>152</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B153" s="3" t="s">
         <v>593</v>
       </c>
       <c r="C153" t="s">
@@ -5856,15 +7124,23 @@
       <c r="F153" t="s">
         <v>13</v>
       </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154">
+      <c r="G153" s="3">
+        <v>0</v>
+      </c>
+      <c r="H153" s="3">
+        <f t="shared" si="5"/>
+        <v>315</v>
+      </c>
+      <c r="I153" s="3">
+        <f t="shared" si="4"/>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
         <v>153</v>
       </c>
-      <c r="B154" t="s">
+      <c r="B154" s="3" t="s">
         <v>597</v>
       </c>
       <c r="C154" t="s">
@@ -5879,15 +7155,23 @@
       <c r="F154" t="s">
         <v>13</v>
       </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155">
+      <c r="G154" s="3">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3">
+        <f t="shared" si="5"/>
+        <v>317</v>
+      </c>
+      <c r="I154" s="3">
+        <f t="shared" si="4"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
         <v>154</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="3" t="s">
         <v>601</v>
       </c>
       <c r="C155" t="s">
@@ -5902,15 +7186,23 @@
       <c r="F155" t="s">
         <v>13</v>
       </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156">
+      <c r="G155" s="3">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3">
+        <f t="shared" si="5"/>
+        <v>319</v>
+      </c>
+      <c r="I155" s="3">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="3">
         <v>155</v>
       </c>
-      <c r="B156" t="s">
+      <c r="B156" s="3" t="s">
         <v>605</v>
       </c>
       <c r="C156" t="s">
@@ -5925,15 +7217,23 @@
       <c r="F156" t="s">
         <v>13</v>
       </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157">
+      <c r="G156" s="3">
+        <v>0</v>
+      </c>
+      <c r="H156" s="3">
+        <f t="shared" si="5"/>
+        <v>321</v>
+      </c>
+      <c r="I156" s="3">
+        <f t="shared" si="4"/>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
         <v>156</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B157" s="3" t="s">
         <v>609</v>
       </c>
       <c r="C157" t="s">
@@ -5948,15 +7248,23 @@
       <c r="F157" t="s">
         <v>13</v>
       </c>
-      <c r="G157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158">
+      <c r="G157" s="3">
+        <v>0</v>
+      </c>
+      <c r="H157" s="3">
+        <f t="shared" si="5"/>
+        <v>323</v>
+      </c>
+      <c r="I157" s="3">
+        <f t="shared" si="4"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
         <v>157</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B158" s="3" t="s">
         <v>612</v>
       </c>
       <c r="C158" t="s">
@@ -5971,15 +7279,23 @@
       <c r="F158" t="s">
         <v>13</v>
       </c>
-      <c r="G158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159">
+      <c r="G158" s="3">
+        <v>0</v>
+      </c>
+      <c r="H158" s="3">
+        <f t="shared" si="5"/>
+        <v>325</v>
+      </c>
+      <c r="I158" s="3">
+        <f t="shared" si="4"/>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
         <v>158</v>
       </c>
-      <c r="B159" t="s">
+      <c r="B159" s="3" t="s">
         <v>616</v>
       </c>
       <c r="C159" t="s">
@@ -5994,15 +7310,23 @@
       <c r="F159" t="s">
         <v>13</v>
       </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160">
+      <c r="G159" s="3">
+        <v>0</v>
+      </c>
+      <c r="H159" s="3">
+        <f t="shared" si="5"/>
+        <v>327</v>
+      </c>
+      <c r="I159" s="3">
+        <f t="shared" si="4"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="3">
         <v>159</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B160" s="3" t="s">
         <v>620</v>
       </c>
       <c r="C160" t="s">
@@ -6017,15 +7341,23 @@
       <c r="F160" t="s">
         <v>61</v>
       </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161">
+      <c r="G160" s="3">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3">
+        <f t="shared" si="5"/>
+        <v>329</v>
+      </c>
+      <c r="I160" s="3">
+        <f t="shared" si="4"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
         <v>160</v>
       </c>
-      <c r="B161" t="s">
+      <c r="B161" s="3" t="s">
         <v>623</v>
       </c>
       <c r="C161" t="s">
@@ -6040,15 +7372,23 @@
       <c r="F161" t="s">
         <v>13</v>
       </c>
-      <c r="G161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162">
+      <c r="G161" s="3">
+        <v>0</v>
+      </c>
+      <c r="H161" s="3">
+        <f t="shared" si="5"/>
+        <v>331</v>
+      </c>
+      <c r="I161" s="3">
+        <f t="shared" si="4"/>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="3">
         <v>161</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="3" t="s">
         <v>627</v>
       </c>
       <c r="C162" t="s">
@@ -6063,39 +7403,55 @@
       <c r="F162" t="s">
         <v>13</v>
       </c>
-      <c r="G162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163">
+      <c r="G162" s="3">
+        <v>0</v>
+      </c>
+      <c r="H162" s="3">
+        <f t="shared" si="5"/>
+        <v>333</v>
+      </c>
+      <c r="I162" s="3">
+        <f t="shared" si="4"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="3">
         <v>162</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B163" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C163" t="s">
+        <v>652</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="G163" s="3">
+        <v>1</v>
+      </c>
+      <c r="H163" s="3">
+        <f t="shared" si="5"/>
+        <v>335</v>
+      </c>
+      <c r="I163" s="3">
+        <f t="shared" si="4"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
+      <c r="B164" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="C163" t="s">
-        <v>634</v>
-      </c>
-      <c r="D163" s="1" t="s">
+      <c r="C164" t="s">
+        <v>640</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>636</v>
-      </c>
-      <c r="G163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>163</v>
-      </c>
-      <c r="B164" t="s">
-        <v>638</v>
-      </c>
-      <c r="C164" t="s">
-        <v>637</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="E164">
         <v>123456</v>
@@ -6103,18 +7459,159 @@
       <c r="F164" t="s">
         <v>13</v>
       </c>
-      <c r="G164">
-        <v>0</v>
-      </c>
+      <c r="G164" s="3">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3">
+        <f t="shared" si="5"/>
+        <v>337</v>
+      </c>
+      <c r="I164" s="3">
+        <f t="shared" si="4"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C165" t="s">
+        <v>634</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E165" t="s">
+        <v>646</v>
+      </c>
+      <c r="F165" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="3">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3">
+        <f t="shared" si="5"/>
+        <v>339</v>
+      </c>
+      <c r="I165" s="3">
+        <f t="shared" si="4"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C166" t="s">
+        <v>641</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E166" t="s">
+        <v>647</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="3">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3">
+        <f t="shared" si="5"/>
+        <v>341</v>
+      </c>
+      <c r="I166" s="3">
+        <f t="shared" si="4"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C167" t="s">
+        <v>642</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="E167" t="s">
+        <v>648</v>
+      </c>
+      <c r="F167" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="3">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3">
+        <f t="shared" si="5"/>
+        <v>343</v>
+      </c>
+      <c r="I167" s="3">
+        <f t="shared" si="4"/>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D164" r:id="rId1" xr:uid="{861EF2FD-EF15-4938-BA5A-3AE163BB2063}"/>
+    <hyperlink ref="D164" r:id="rId1" xr:uid="{C4DC3310-9C62-4BD6-93E4-C0398C5C7B70}"/>
+    <hyperlink ref="D165" r:id="rId2" xr:uid="{06A8AD21-B5C6-4F51-8E41-18A1D2C11E29}"/>
+    <hyperlink ref="D166" r:id="rId3" xr:uid="{33955FCA-93EC-4B67-AFC3-B1C595059228}"/>
+    <hyperlink ref="D167" r:id="rId4" xr:uid="{B0EFAAB2-F28A-40DD-AA2E-8F73F3D34C67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <ignoredErrors>
-    <ignoredError sqref="A2:F162 A1:D1" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>